--- a/test-case/系统测试用例.xlsx
+++ b/test-case/系统测试用例.xlsx
@@ -4,26 +4,2408 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="24750" windowHeight="10480"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="功能测试用例" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">功能测试用例!$A$1:$J$150</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="698">
+  <si>
+    <t>用例编号</t>
+  </si>
+  <si>
+    <t>所属模块</t>
+  </si>
+  <si>
+    <t>用例标题</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>前置条件</t>
+  </si>
+  <si>
+    <t>操作步骤</t>
+  </si>
+  <si>
+    <t>预期结果</t>
+  </si>
+  <si>
+    <t>实际结果</t>
+  </si>
+  <si>
+    <t>测试结果</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>LOGIN-001</t>
+  </si>
+  <si>
+    <t>登录认证模块</t>
+  </si>
+  <si>
+    <t>登录页界面元素完整展示-页面元素齐全</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>系统已部署运行，未登录状态</t>
+  </si>
+  <si>
+    <t>1. 打开浏览器访问系统登录页URL
+2. 检查页面元素是否齐全</t>
+  </si>
+  <si>
+    <t>用户名输入框、密码输入框、验证码输入框、登录按钮、记住我选项均正常展示，页面布局无错乱</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>LOGIN-002</t>
+  </si>
+  <si>
+    <t>输入框占位提示文字正确展示-提示语规范</t>
+  </si>
+  <si>
+    <t>已打开登录页</t>
+  </si>
+  <si>
+    <t>1. 查看用户名输入框占位提示
+2. 查看密码输入框占位提示
+3. 查看验证码输入框占位提示</t>
+  </si>
+  <si>
+    <t>各输入框占位提示文字正确规范，无乱码或缺失</t>
+  </si>
+  <si>
+    <t>LOGIN-003</t>
+  </si>
+  <si>
+    <t>验证码图片正常加载-图片显示清晰</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>1. 访问登录页
+2. 查看验证码图片区域</t>
+  </si>
+  <si>
+    <t>验证码图片正常加载显示，字符清晰可辨，无裂图或空白</t>
+  </si>
+  <si>
+    <t>LOGIN-004</t>
+  </si>
+  <si>
+    <t>点击验证码图片刷新-验证码更新</t>
+  </si>
+  <si>
+    <t>已打开登录页，验证码已加载</t>
+  </si>
+  <si>
+    <t>1. 记录当前验证码内容
+2. 点击验证码图片</t>
+  </si>
+  <si>
+    <t>验证码图片刷新，生成新的验证码，与原验证码不同</t>
+  </si>
+  <si>
+    <t>LOGIN-005</t>
+  </si>
+  <si>
+    <t>登录按钮悬停样式反馈-交互样式正常</t>
+  </si>
+  <si>
+    <t>1. 鼠标移至登录按钮上方
+2. 观察按钮样式变化</t>
+  </si>
+  <si>
+    <t>登录按钮默认状态正常，鼠标悬停时有明显样式反馈（颜色或阴影变化）</t>
+  </si>
+  <si>
+    <t>LOGIN-006</t>
+  </si>
+  <si>
+    <t>正确账号密码验证码登录-登录成功跳转首页</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>已存在有效账号且状态正常</t>
+  </si>
+  <si>
+    <t>1. 输入正确的用户名
+2. 输入正确的密码
+3. 输入正确的验证码
+4. 点击登录按钮</t>
+  </si>
+  <si>
+    <t>登录成功，页面跳转至系统首页，系统正常加载</t>
+  </si>
+  <si>
+    <t>LOGIN-007</t>
+  </si>
+  <si>
+    <t>勾选记住我重开浏览器-用户名自动填充</t>
+  </si>
+  <si>
+    <t>已存在有效账号</t>
+  </si>
+  <si>
+    <t>1. 输入正确用户名、密码、验证码
+2. 勾选「记住我」
+3. 点击登录成功
+4. 关闭浏览器
+5. 重新打开浏览器访问登录页</t>
+  </si>
+  <si>
+    <t>登录页用户名输入框自动填充上次登录的用户名</t>
+  </si>
+  <si>
+    <t>LOGIN-008</t>
+  </si>
+  <si>
+    <t>登录成功左侧菜单按权限加载-菜单正常展示</t>
+  </si>
+  <si>
+    <t>已存在带菜单权限的账号</t>
+  </si>
+  <si>
+    <t>1. 使用该账号正确登录系统
+2. 查看左侧菜单区域</t>
+  </si>
+  <si>
+    <t>登录成功后，左侧菜单根据当前用户权限正常加载展示，无权限菜单不显示</t>
+  </si>
+  <si>
+    <t>LOGIN-009</t>
+  </si>
+  <si>
+    <t>登录成功右上角显示用户昵称-用户信息展示</t>
+  </si>
+  <si>
+    <t>已存在有效账号且有昵称</t>
+  </si>
+  <si>
+    <t>1. 使用该账号正确登录系统
+2. 查看页面右上角区域</t>
+  </si>
+  <si>
+    <t>右上角正确显示当前登录用户的昵称</t>
+  </si>
+  <si>
+    <t>LOGIN-010</t>
+  </si>
+  <si>
+    <t>退出登录返回登录页-Token失效</t>
+  </si>
+  <si>
+    <t>已成功登录系统</t>
+  </si>
+  <si>
+    <t>1. 点击右上角退出登录按钮
+2. 观察页面跳转</t>
+  </si>
+  <si>
+    <t>成功返回登录页，原Token失效，无法继续访问系统内部页面</t>
+  </si>
+  <si>
+    <t>LOGIN-011</t>
+  </si>
+  <si>
+    <t>用户名为空登录-提示请输入用户名</t>
+  </si>
+  <si>
+    <t>1. 用户名输入框留空
+2. 输入密码与验证码
+3. 点击登录按钮</t>
+  </si>
+  <si>
+    <t>登录失败，提示「请输入用户名」，不发起登录请求</t>
+  </si>
+  <si>
+    <t>LOGIN-012</t>
+  </si>
+  <si>
+    <t>密码为空登录-提示请输入用户密码</t>
+  </si>
+  <si>
+    <t>1. 输入正确用户名
+2. 密码输入框留空
+3. 输入验证码
+4. 点击登录按钮</t>
+  </si>
+  <si>
+    <t>登录失败，提示「请输入用户密码」，不发起登录请求</t>
+  </si>
+  <si>
+    <t>LOGIN-013</t>
+  </si>
+  <si>
+    <t>验证码为空登录-提示请输入验证码</t>
+  </si>
+  <si>
+    <t>1. 输入正确用户名与密码
+2. 验证码输入框留空
+3. 点击登录按钮</t>
+  </si>
+  <si>
+    <t>登录失败，提示「请输入验证码」，不发起登录请求</t>
+  </si>
+  <si>
+    <t>LOGIN-014</t>
+  </si>
+  <si>
+    <t>用户名错误登录-提示用户不存在/密码错误</t>
+  </si>
+  <si>
+    <t>1. 输入不存在的用户名
+2. 输入任意密码
+3. 输入正确验证码
+4. 点击登录按钮</t>
+  </si>
+  <si>
+    <t>登录失败，提示「用户不存在/密码错误」</t>
+  </si>
+  <si>
+    <t>LOGIN-015</t>
+  </si>
+  <si>
+    <t>密码错误登录-提示用户不存在/密码错误</t>
+  </si>
+  <si>
+    <t>1. 输入正确用户名
+2. 输入错误密码
+3. 输入正确验证码
+4. 点击登录按钮</t>
+  </si>
+  <si>
+    <t>LOGIN-016</t>
+  </si>
+  <si>
+    <t>验证码错误登录-提示验证码错误</t>
+  </si>
+  <si>
+    <t>1. 输入正确用户名与密码
+2. 输入错误验证码
+3. 点击登录按钮</t>
+  </si>
+  <si>
+    <t>登录失败，提示「验证码错误」</t>
+  </si>
+  <si>
+    <t>LOGIN-017</t>
+  </si>
+  <si>
+    <t>账号被禁用登录-提示账号已停用</t>
+  </si>
+  <si>
+    <t>已存在被停用的账号</t>
+  </si>
+  <si>
+    <t>1. 输入被停用账号的正确用户名与密码
+2. 输入正确验证码
+3. 点击登录按钮</t>
+  </si>
+  <si>
+    <t>登录失败，提示「账号已停用」，无法登录系统</t>
+  </si>
+  <si>
+    <t>LOGIN-018</t>
+  </si>
+  <si>
+    <t>连续多次登录失败-触发防暴力破解拦截</t>
+  </si>
+  <si>
+    <t>1. 连续输入错误密码登录达到系统设定次数
+2. 再次尝试登录</t>
+  </si>
+  <si>
+    <t>系统触发防暴力破解拦截，账号被锁定或限制登录，并给出提示</t>
+  </si>
+  <si>
+    <t>LOGIN-019</t>
+  </si>
+  <si>
+    <t>未登录访问内部页面-重定向到登录页</t>
+  </si>
+  <si>
+    <t>未登录状态</t>
+  </si>
+  <si>
+    <t>1. 未登录状态下直接在地址栏输入系统内部页面URL
+2. 访问该URL</t>
+  </si>
+  <si>
+    <t>页面自动重定向到登录页，无法直接访问内部页面</t>
+  </si>
+  <si>
+    <t>LOGIN-020</t>
+  </si>
+  <si>
+    <t>登录成功生成有效Token-请求头携带正常</t>
+  </si>
+  <si>
+    <t>1. 正确登录系统
+2. 打开浏览器开发者工具网络面板
+3. 触发任意接口请求查看请求头</t>
+  </si>
+  <si>
+    <t>登录成功后生成有效Token，后续请求头中正常携带Token字段</t>
+  </si>
+  <si>
+    <t>LOGIN-021</t>
+  </si>
+  <si>
+    <t>退出登录后原Token失效-无法访问接口</t>
+  </si>
+  <si>
+    <t>1. 登录系统后获取当前Token
+2. 点击退出登录
+3. 使用原Token发起接口请求</t>
+  </si>
+  <si>
+    <t>原Token已失效，接口请求返回未授权或重定向登录，无法继续访问</t>
+  </si>
+  <si>
+    <t>LOGIN-022</t>
+  </si>
+  <si>
+    <t>不同角色登录菜单按钮权限不一致-权限隔离正常</t>
+  </si>
+  <si>
+    <t>已存在不同角色账号（如管理员、普通用户）</t>
+  </si>
+  <si>
+    <t>1. 使用管理员账号登录，记录可见菜单与按钮
+2. 退出后使用普通用户账号登录
+3. 对比可见菜单与按钮</t>
+  </si>
+  <si>
+    <t>不同角色账号登录展示的菜单、按钮权限不一致，符合各角色权限配置</t>
+  </si>
+  <si>
+    <t>LOGIN-023</t>
+  </si>
+  <si>
+    <t>无权限菜单URL直接访问-提示无权限或404</t>
+  </si>
+  <si>
+    <t>已登录但无某菜单权限的账号</t>
+  </si>
+  <si>
+    <t>1. 使用无某菜单权限的账号登录
+2. 在地址栏输入该菜单对应URL访问</t>
+  </si>
+  <si>
+    <t>页面提示无权限或跳转404页面，无法正常访问该菜单</t>
+  </si>
+  <si>
+    <t>LOGIN-024</t>
+  </si>
+  <si>
+    <t>Chrome浏览器登录与展示-功能正常</t>
+  </si>
+  <si>
+    <t>Chrome浏览器环境</t>
+  </si>
+  <si>
+    <t>1. 使用Chrome浏览器访问登录页
+2. 执行正常登录流程</t>
+  </si>
+  <si>
+    <t>Chrome浏览器下登录功能正常，页面展示无异常</t>
+  </si>
+  <si>
+    <t>LOGIN-025</t>
+  </si>
+  <si>
+    <t>页面缩放不影响登录功能-功能正常使用</t>
+  </si>
+  <si>
+    <t>1. 对浏览器页面进行缩放（如75%、125%）
+2. 执行登录操作</t>
+  </si>
+  <si>
+    <t>页面缩放后登录功能正常使用，布局无严重错乱</t>
+  </si>
+  <si>
+    <t>LOGIN-026</t>
+  </si>
+  <si>
+    <t>用户名输入最大长度边界值-超长拦截</t>
+  </si>
+  <si>
+    <t>1. 在用户名输入框输入超过最大长度限制的字符
+2. 输入密码与验证码
+3. 点击登录</t>
+  </si>
+  <si>
+    <t>输入框按最大长度限制截断或提示长度限制，不出现异常</t>
+  </si>
+  <si>
+    <t>LOGIN-027</t>
+  </si>
+  <si>
+    <t>密码输入最小长度边界值-长度校验生效</t>
+  </si>
+  <si>
+    <t>1. 输入正确用户名
+2. 输入小于最小长度要求的密码
+3. 输入正确验证码
+4. 点击登录</t>
+  </si>
+  <si>
+    <t>登录失败，提示密码长度不符合要求或用户不存在/密码错误</t>
+  </si>
+  <si>
+    <t>LOGIN-028</t>
+  </si>
+  <si>
+    <t>验证码大小写不一致-提示验证码错误</t>
+  </si>
+  <si>
+    <t>1. 输入正确用户名与密码
+2. 输入验证码但大小写与图片不一致
+3. 点击登录</t>
+  </si>
+  <si>
+    <t>USER-001</t>
+  </si>
+  <si>
+    <t>用户管理模块</t>
+  </si>
+  <si>
+    <t>用户列表字段完整展示-字段齐全</t>
+  </si>
+  <si>
+    <t>已登录且有用户管理列表查看权限</t>
+  </si>
+  <si>
+    <t>1. 进入用户管理列表页
+2. 检查列表字段</t>
+  </si>
+  <si>
+    <t>列表完整展示用户编号、用户名、用户昵称、部门、手机号、状态、创建时间、操作列</t>
+  </si>
+  <si>
+    <t>USER-002</t>
+  </si>
+  <si>
+    <t>顶部查询区域元素完整-查询条件齐全</t>
+  </si>
+  <si>
+    <t>已进入用户管理列表页</t>
+  </si>
+  <si>
+    <t>1. 查看顶部查询区域元素</t>
+  </si>
+  <si>
+    <t>用户名、手机号、状态、部门选择、查询按钮、重置按钮均正常展示</t>
+  </si>
+  <si>
+    <t>USER-003</t>
+  </si>
+  <si>
+    <t>操作按钮按权限展示-权限控制正常</t>
+  </si>
+  <si>
+    <t>已登录账号具备部分操作权限</t>
+  </si>
+  <si>
+    <t>1. 使用对应权限账号进入用户管理页
+2. 查看操作按钮展示情况</t>
+  </si>
+  <si>
+    <t>新增、修改、删除、导入、导出按钮按当前账号权限正常展示或隐藏</t>
+  </si>
+  <si>
+    <t>USER-004</t>
+  </si>
+  <si>
+    <t>分页每页条数切换生效-分页正常</t>
+  </si>
+  <si>
+    <t>用户列表数据量大于默认每页条数</t>
+  </si>
+  <si>
+    <t>1. 进入用户管理列表页
+2. 切换每页条数（如10/20/50）
+3. 查看列表数据与总条数</t>
+  </si>
+  <si>
+    <t>每页条数切换生效，列表数据按条数展示，总条数显示正确</t>
+  </si>
+  <si>
+    <t>USER-005</t>
+  </si>
+  <si>
+    <t>列表数据与数据库一致-数据准确</t>
+  </si>
+  <si>
+    <t>数据库存在用户数据</t>
+  </si>
+  <si>
+    <t>1. 查询数据库用户表数据
+2. 进入用户管理列表页对比展示数据</t>
+  </si>
+  <si>
+    <t>列表展示数据与数据库中数据一致，无遗漏或多余</t>
+  </si>
+  <si>
+    <t>USER-006</t>
+  </si>
+  <si>
+    <t>用户名模糊查询-正确过滤匹配数据</t>
+  </si>
+  <si>
+    <t>列表存在多条用户数据</t>
+  </si>
+  <si>
+    <t>1. 在查询区用户名输入框输入部分关键字
+2. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表正确过滤展示包含该关键字的用户数据</t>
+  </si>
+  <si>
+    <t>USER-007</t>
+  </si>
+  <si>
+    <t>手机号精确查询-精准匹配对应记录</t>
+  </si>
+  <si>
+    <t>列表存在对应用户数据</t>
+  </si>
+  <si>
+    <t>1. 在查询区输入完整手机号
+2. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表精准匹配展示对应手机号的用户记录</t>
+  </si>
+  <si>
+    <t>USER-008</t>
+  </si>
+  <si>
+    <t>状态下拉查询-列表数据对应过滤</t>
+  </si>
+  <si>
+    <t>列表存在正常与停用状态用户</t>
+  </si>
+  <si>
+    <t>1. 在查询区状态下拉选择「正常」
+2. 点击查询
+3. 切换为「停用」再次查询</t>
+  </si>
+  <si>
+    <t>选择正常时仅展示状态正常的用户，选择停用时仅展示停用用户</t>
+  </si>
+  <si>
+    <t>USER-009</t>
+  </si>
+  <si>
+    <t>部门树形选择查询-展示该部门下用户</t>
+  </si>
+  <si>
+    <t>存在多层级部门及对应用户</t>
+  </si>
+  <si>
+    <t>1. 在查询区点击部门选择树
+2. 选择指定部门
+3. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表展示所选部门下的用户数据</t>
+  </si>
+  <si>
+    <t>USER-010</t>
+  </si>
+  <si>
+    <t>组合条件查询-多条件同时生效</t>
+  </si>
+  <si>
+    <t>列表存在满足组合条件的数据</t>
+  </si>
+  <si>
+    <t>1. 同时输入用户名关键字
+2. 选择状态
+3. 选择部门
+4. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表展示同时满足用户名、状态、部门条件的数据，多条件同时生效</t>
+  </si>
+  <si>
+    <t>USER-011</t>
+  </si>
+  <si>
+    <t>重置按钮清空查询条件-恢复全量展示</t>
+  </si>
+  <si>
+    <t>已执行查询且查询条件有值</t>
+  </si>
+  <si>
+    <t>1. 点击查询区重置按钮
+2. 查看查询条件与列表数据</t>
+  </si>
+  <si>
+    <t>所有查询条件清空，列表恢复全量数据展示</t>
+  </si>
+  <si>
+    <t>USER-012</t>
+  </si>
+  <si>
+    <t>空查询结果-提示无数据</t>
+  </si>
+  <si>
+    <t>列表存在数据</t>
+  </si>
+  <si>
+    <t>1. 在查询区输入不存在的关键字
+2. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表为空，提示「无数据」或空状态图</t>
+  </si>
+  <si>
+    <t>USER-013</t>
+  </si>
+  <si>
+    <t>新增用户填写合法必填项-提交成功新增数据</t>
+  </si>
+  <si>
+    <t>已登录且有新增权限</t>
+  </si>
+  <si>
+    <t>1. 点击新增按钮
+2. 填写所有合法必填项（用户名、密码、昵称等）
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交成功，列表新增一条对应数据，提示新增成功</t>
+  </si>
+  <si>
+    <t>USER-014</t>
+  </si>
+  <si>
+    <t>新增用户名为空-输入框红色提示</t>
+  </si>
+  <si>
+    <t>已打开新增用户弹窗</t>
+  </si>
+  <si>
+    <t>1. 用户名输入框留空
+2. 填写其他必填项
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，用户名输入框下方红色提示必填，不发起请求</t>
+  </si>
+  <si>
+    <t>USER-015</t>
+  </si>
+  <si>
+    <t>新增密码为空-输入框红色提示</t>
+  </si>
+  <si>
+    <t>1. 密码输入框留空
+2. 填写其他必填项
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，密码输入框下方红色提示必填，不发起请求</t>
+  </si>
+  <si>
+    <t>USER-016</t>
+  </si>
+  <si>
+    <t>新增昵称为空-输入框红色提示</t>
+  </si>
+  <si>
+    <t>1. 昵称输入框留空
+2. 填写其他必填项
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，昵称输入框下方红色提示必填，不发起请求</t>
+  </si>
+  <si>
+    <t>USER-017</t>
+  </si>
+  <si>
+    <t>用户名重复-提示用户名已存在</t>
+  </si>
+  <si>
+    <t>已存在对应用户名的用户</t>
+  </si>
+  <si>
+    <t>1. 点击新增按钮
+2. 输入已存在的用户名
+3. 填写其他合法必填项
+4. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，提示「用户名已存在」，不新增数据</t>
+  </si>
+  <si>
+    <t>USER-018</t>
+  </si>
+  <si>
+    <t>邮箱格式非法-提示请输入正确的邮箱</t>
+  </si>
+  <si>
+    <t>1. 填写合法必填项
+2. 邮箱输入非法格式（如abc@）
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，提示「请输入正确的邮箱地址」</t>
+  </si>
+  <si>
+    <t>USER-019</t>
+  </si>
+  <si>
+    <t>手机号非11位-提示格式错误</t>
+  </si>
+  <si>
+    <t>1. 填写合法必填项
+2. 手机号输入非11位数字（如123456）
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，提示手机号格式错误</t>
+  </si>
+  <si>
+    <t>USER-020</t>
+  </si>
+  <si>
+    <t>手机号非法号段-提示格式错误</t>
+  </si>
+  <si>
+    <t>1. 填写合法必填项
+2. 手机号输入非法号段11位数字（如00000000000）
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>USER-021</t>
+  </si>
+  <si>
+    <t>密码过短过于简单-提示密码强度要求</t>
+  </si>
+  <si>
+    <t>1. 填写合法必填项
+2. 密码输入过短或过于简单（如123）
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，提示密码强度要求</t>
+  </si>
+  <si>
+    <t>USER-022</t>
+  </si>
+  <si>
+    <t>新增取消按钮-关闭弹窗不保存数据</t>
+  </si>
+  <si>
+    <t>已打开新增用户弹窗且已填写数据</t>
+  </si>
+  <si>
+    <t>1. 在新增弹窗填写部分数据
+2. 点击取消按钮</t>
+  </si>
+  <si>
+    <t>弹窗关闭，数据不保存，列表无新增</t>
+  </si>
+  <si>
+    <t>USER-023</t>
+  </si>
+  <si>
+    <t>新增弹窗重置按钮-清空已填内容</t>
+  </si>
+  <si>
+    <t>1. 在新增弹窗填写部分数据
+2. 点击重置按钮</t>
+  </si>
+  <si>
+    <t>弹窗内所有已填内容清空</t>
+  </si>
+  <si>
+    <t>USER-024</t>
+  </si>
+  <si>
+    <t>编辑用户信息-提交后列表同步更新</t>
+  </si>
+  <si>
+    <t>列表存在可编辑用户</t>
+  </si>
+  <si>
+    <t>1. 点击某用户操作列修改按钮
+2. 修改昵称、手机号、邮箱等信息
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交成功，列表对应记录信息同步更新，提示修改成功</t>
+  </si>
+  <si>
+    <t>USER-025</t>
+  </si>
+  <si>
+    <t>编辑时用户名修改为重复-系统拦截</t>
+  </si>
+  <si>
+    <t>列表存在多个用户</t>
+  </si>
+  <si>
+    <t>1. 点击某用户修改按钮
+2. 将用户名修改为已存在的其他用户名
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，系统拦截并提示用户名已存在或用户名不可修改</t>
+  </si>
+  <si>
+    <t>USER-026</t>
+  </si>
+  <si>
+    <t>禁用用户后账号无法登录-停用生效</t>
+  </si>
+  <si>
+    <t>列表存在状态正常的用户</t>
+  </si>
+  <si>
+    <t>1. 点击某用户修改按钮
+2. 将状态切换为停用
+3. 提交保存
+4. 使用该账号尝试登录</t>
+  </si>
+  <si>
+    <t>提交成功后该账号状态为停用，使用该账号登录提示账号已停用，无法登录</t>
+  </si>
+  <si>
+    <t>USER-027</t>
+  </si>
+  <si>
+    <t>启用用户后恢复登录权限-启用生效</t>
+  </si>
+  <si>
+    <t>列表存在状态停用的用户</t>
+  </si>
+  <si>
+    <t>1. 点击某停用用户修改按钮
+2. 将状态切换为正常
+3. 提交保存
+4. 使用该账号尝试登录</t>
+  </si>
+  <si>
+    <t>提交成功后该账号状态为正常，使用正确账密可成功登录</t>
+  </si>
+  <si>
+    <t>USER-028</t>
+  </si>
+  <si>
+    <t>重置密码二次确认-密码重置为默认值</t>
+  </si>
+  <si>
+    <t>列表存在对应用户</t>
+  </si>
+  <si>
+    <t>1. 点击某用户操作列重置密码按钮
+2. 在二次确认框点击确认
+3. 使用默认密码尝试登录</t>
+  </si>
+  <si>
+    <t>密码重置为默认值，使用默认密码可成功登录，提示重置成功</t>
+  </si>
+  <si>
+    <t>USER-029</t>
+  </si>
+  <si>
+    <t>编辑取消-数据不发生变化</t>
+  </si>
+  <si>
+    <t>1. 点击某用户修改按钮
+2. 修改部分信息
+3. 点击取消按钮</t>
+  </si>
+  <si>
+    <t>弹窗关闭，数据不发生变化，列表保持原数据</t>
+  </si>
+  <si>
+    <t>USER-030</t>
+  </si>
+  <si>
+    <t>单条删除二次确认-删除成功移除数据</t>
+  </si>
+  <si>
+    <t>列表存在可删除用户</t>
+  </si>
+  <si>
+    <t>1. 点击某用户操作列删除按钮
+2. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>删除成功，列表移除该条数据，提示删除成功</t>
+  </si>
+  <si>
+    <t>USER-031</t>
+  </si>
+  <si>
+    <t>批量删除多条-选中数据均被移除</t>
+  </si>
+  <si>
+    <t>列表存在多条可删除用户</t>
+  </si>
+  <si>
+    <t>1. 勾选多条用户数据
+2. 点击批量删除按钮
+3. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>删除成功，所有选中数据均从列表移除，提示删除成功</t>
+  </si>
+  <si>
+    <t>USER-032</t>
+  </si>
+  <si>
+    <t>删除当前登录账号-系统拦截提示</t>
+  </si>
+  <si>
+    <t>已登录某账号且该账号在列表中</t>
+  </si>
+  <si>
+    <t>1. 在列表找到当前登录账号
+2. 点击其删除按钮
+3. 确认删除</t>
+  </si>
+  <si>
+    <t>系统拦截删除操作，提示不允许删除当前登录账号</t>
+  </si>
+  <si>
+    <t>USER-033</t>
+  </si>
+  <si>
+    <t>删除二次确认取消-数据不删除</t>
+  </si>
+  <si>
+    <t>1. 点击某用户删除按钮
+2. 在二次确认框点击取消</t>
+  </si>
+  <si>
+    <t>确认框关闭，数据不删除，列表保持原数据</t>
+  </si>
+  <si>
+    <t>USER-034</t>
+  </si>
+  <si>
+    <t>删除用户后角色权限数据同步清理-数据一致</t>
+  </si>
+  <si>
+    <t>列表存在已分配角色的用户</t>
+  </si>
+  <si>
+    <t>1. 删除某已分配角色的用户
+2. 查询角色管理中该用户关联数据</t>
+  </si>
+  <si>
+    <t>删除成功后，该用户对应的角色关联、权限数据同步清理，数据一致</t>
+  </si>
+  <si>
+    <t>USER-035</t>
+  </si>
+  <si>
+    <t>导出全部-Excel内容与列表一致</t>
+  </si>
+  <si>
+    <t>列表存在用户数据</t>
+  </si>
+  <si>
+    <t>1. 不勾选任何数据
+2. 点击导出按钮
+3. 打开下载的Excel文件</t>
+  </si>
+  <si>
+    <t>成功下载Excel文件，内容与列表当前数据一致</t>
+  </si>
+  <si>
+    <t>USER-036</t>
+  </si>
+  <si>
+    <t>导出选中-仅包含选中数据</t>
+  </si>
+  <si>
+    <t>1. 勾选部分用户数据
+2. 点击导出按钮
+3. 打开下载的Excel文件</t>
+  </si>
+  <si>
+    <t>成功下载Excel文件，仅包含勾选选中的数据</t>
+  </si>
+  <si>
+    <t>USER-037</t>
+  </si>
+  <si>
+    <t>模板下载-下载标准导入模板</t>
+  </si>
+  <si>
+    <t>已进入用户管理页</t>
+  </si>
+  <si>
+    <t>1. 点击导入按钮
+2. 在导入弹窗点击下载模板</t>
+  </si>
+  <si>
+    <t>成功下载标准导入模板文件，模板字段完整</t>
+  </si>
+  <si>
+    <t>USER-038</t>
+  </si>
+  <si>
+    <t>正常导入按模板-新增对应记录</t>
+  </si>
+  <si>
+    <t>已下载并按模板填写合法数据</t>
+  </si>
+  <si>
+    <t>1. 点击导入按钮
+2. 上传按模板填写的合法数据文件
+3. 点击确定</t>
+  </si>
+  <si>
+    <t>导入成功，列表新增对应记录，提示导入成功及数量</t>
+  </si>
+  <si>
+    <t>USER-039</t>
+  </si>
+  <si>
+    <t>异常导入格式错误-提示导入失败原因</t>
+  </si>
+  <si>
+    <t>已准备格式错误或必填项缺失的文件</t>
+  </si>
+  <si>
+    <t>1. 点击导入按钮
+2. 上传格式错误或必填项缺失的文件
+3. 点击确定</t>
+  </si>
+  <si>
+    <t>导入失败，提示导入失败原因及具体错误行</t>
+  </si>
+  <si>
+    <t>USER-040</t>
+  </si>
+  <si>
+    <t>无新增权限-隐藏新增按钮</t>
+  </si>
+  <si>
+    <t>已登录账号无新增权限</t>
+  </si>
+  <si>
+    <t>1. 使用无新增权限账号进入用户管理页
+2. 查看新增按钮</t>
+  </si>
+  <si>
+    <t>新增按钮隐藏，不展示</t>
+  </si>
+  <si>
+    <t>USER-041</t>
+  </si>
+  <si>
+    <t>无删除权限-隐藏删除与批量删除按钮</t>
+  </si>
+  <si>
+    <t>已登录账号无删除权限</t>
+  </si>
+  <si>
+    <t>1. 使用无删除权限账号进入用户管理页
+2. 查看删除与批量删除按钮</t>
+  </si>
+  <si>
+    <t>删除与批量删除按钮隐藏，不展示</t>
+  </si>
+  <si>
+    <t>USER-042</t>
+  </si>
+  <si>
+    <t>无编辑权限-隐藏修改按钮</t>
+  </si>
+  <si>
+    <t>已登录账号无编辑权限</t>
+  </si>
+  <si>
+    <t>1. 使用无编辑权限账号进入用户管理页
+2. 查看修改按钮</t>
+  </si>
+  <si>
+    <t>修改按钮隐藏，不展示</t>
+  </si>
+  <si>
+    <t>USER-043</t>
+  </si>
+  <si>
+    <t>普通用户无法查看管理员敏感操作-权限隔离</t>
+  </si>
+  <si>
+    <t>已登录普通用户账号</t>
+  </si>
+  <si>
+    <t>1. 使用普通用户账号进入用户管理页
+2. 查看管理员账号操作选项</t>
+  </si>
+  <si>
+    <t>普通用户无法查看管理员账号的敏感操作选项</t>
+  </si>
+  <si>
+    <t>USER-044</t>
+  </si>
+  <si>
+    <t>用户名长度边界值-边界校验生效</t>
+  </si>
+  <si>
+    <t>1. 用户名输入最小长度边界值提交
+2. 用户名输入最大长度边界值提交
+3. 用户名输入超过最大长度提交</t>
+  </si>
+  <si>
+    <t>边界值内提交成功，超过最大长度被拦截或截断并提示</t>
+  </si>
+  <si>
+    <t>USER-045</t>
+  </si>
+  <si>
+    <t>手机号11位边界值-边界校验生效</t>
+  </si>
+  <si>
+    <t>1. 手机号输入10位提交
+2. 手机号输入11位合法号段提交
+3. 手机号输入12位提交</t>
+  </si>
+  <si>
+    <t>10位与12位提示格式错误，11位合法号段提交成功</t>
+  </si>
+  <si>
+    <t>ROLE-001</t>
+  </si>
+  <si>
+    <t>角色管理模块</t>
+  </si>
+  <si>
+    <t>角色列表字段完整展示-字段齐全</t>
+  </si>
+  <si>
+    <t>已登录且有角色管理查看权限</t>
+  </si>
+  <si>
+    <t>1. 进入角色管理列表页
+2. 检查列表字段</t>
+  </si>
+  <si>
+    <t>列表完整展示角色编号、角色名称、角色权限字符串、显示排序、状态、创建时间、操作列</t>
+  </si>
+  <si>
+    <t>ROLE-002</t>
+  </si>
+  <si>
+    <t>查询区域元素完整-查询条件齐全</t>
+  </si>
+  <si>
+    <t>已进入角色管理列表页</t>
+  </si>
+  <si>
+    <t>1. 查看查询区域元素</t>
+  </si>
+  <si>
+    <t>角色名称、角色状态、查询、重置按钮均正常展示</t>
+  </si>
+  <si>
+    <t>ROLE-003</t>
+  </si>
+  <si>
+    <t>角色名称模糊查询-正常过滤</t>
+  </si>
+  <si>
+    <t>列表存在多条角色数据</t>
+  </si>
+  <si>
+    <t>1. 在查询区角色名称输入部分关键字
+2. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表正确过滤展示包含该关键字的角色数据</t>
+  </si>
+  <si>
+    <t>ROLE-004</t>
+  </si>
+  <si>
+    <t>角色状态筛选-正常过滤</t>
+  </si>
+  <si>
+    <t>列表存在正常与停用状态角色</t>
+  </si>
+  <si>
+    <t>1. 在查询区状态下拉选择某状态
+2. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表展示对应状态的角色数据</t>
+  </si>
+  <si>
+    <t>ROLE-005</t>
+  </si>
+  <si>
+    <t>重置按钮清空查询条件-恢复正常展示</t>
+  </si>
+  <si>
+    <t>ROLE-006</t>
+  </si>
+  <si>
+    <t>分页每页条数切换-分页正常</t>
+  </si>
+  <si>
+    <t>角色列表数据量大于默认每页条数</t>
+  </si>
+  <si>
+    <t>1. 进入角色管理列表页
+2. 切换每页条数
+3. 查看列表数据与总条数</t>
+  </si>
+  <si>
+    <t>ROLE-007</t>
+  </si>
+  <si>
+    <t>新增角色合法数据-提交成功</t>
+  </si>
+  <si>
+    <t>1. 点击新增按钮
+2. 填写合法角色名称、权限字符、排序
+3. 选择状态
+4. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交成功，列表新增对应角色数据，提示新增成功</t>
+  </si>
+  <si>
+    <t>ROLE-008</t>
+  </si>
+  <si>
+    <t>角色名称为空-必填提示</t>
+  </si>
+  <si>
+    <t>已打开新增角色弹窗</t>
+  </si>
+  <si>
+    <t>1. 角色名称留空
+2. 填写其他必填项
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，角色名称必填提示，不发起请求</t>
+  </si>
+  <si>
+    <t>ROLE-009</t>
+  </si>
+  <si>
+    <t>权限字符为空-必填提示</t>
+  </si>
+  <si>
+    <t>1. 权限字符留空
+2. 填写其他必填项
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，权限字符必填提示，不发起请求</t>
+  </si>
+  <si>
+    <t>ROLE-010</t>
+  </si>
+  <si>
+    <t>角色名称重复-提示重复</t>
+  </si>
+  <si>
+    <t>已存在对应角色名称</t>
+  </si>
+  <si>
+    <t>1. 点击新增按钮
+2. 输入已存在的角色名称
+3. 填写其他合法项
+4. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，提示角色名称重复，不新增数据</t>
+  </si>
+  <si>
+    <t>ROLE-011</t>
+  </si>
+  <si>
+    <t>新增角色分配菜单权限-保存后生效</t>
+  </si>
+  <si>
+    <t>1. 填写合法角色信息
+2. 勾选对应菜单权限
+3. 点击确定提交
+4. 使用该角色账号登录验证</t>
+  </si>
+  <si>
+    <t>提交成功，权限配置生效，对应账号登录可见所分配菜单</t>
+  </si>
+  <si>
+    <t>ROLE-012</t>
+  </si>
+  <si>
+    <t>取消新增-不保存数据</t>
+  </si>
+  <si>
+    <t>已打开新增角色弹窗且已填写数据</t>
+  </si>
+  <si>
+    <t>ROLE-013</t>
+  </si>
+  <si>
+    <t>编辑角色信息-提交后列表同步更新</t>
+  </si>
+  <si>
+    <t>列表存在可编辑角色</t>
+  </si>
+  <si>
+    <t>1. 点击某角色修改按钮
+2. 修改角色名称、排序、状态
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>ROLE-014</t>
+  </si>
+  <si>
+    <t>单条删除角色二次确认-删除成功</t>
+  </si>
+  <si>
+    <t>列表存在可删除角色</t>
+  </si>
+  <si>
+    <t>1. 点击某角色删除按钮
+2. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>删除成功，列表移除该角色数据，提示删除成功</t>
+  </si>
+  <si>
+    <t>ROLE-015</t>
+  </si>
+  <si>
+    <t>批量删除角色-删除成功</t>
+  </si>
+  <si>
+    <t>列表存在多条可删除角色</t>
+  </si>
+  <si>
+    <t>1. 勾选多条角色数据
+2. 点击批量删除按钮
+3. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>删除成功，所有选中角色均从列表移除，提示删除成功</t>
+  </si>
+  <si>
+    <t>ROLE-016</t>
+  </si>
+  <si>
+    <t>已分配用户的角色删除-提示或级联处理</t>
+  </si>
+  <si>
+    <t>列表存在已分配用户的角色</t>
+  </si>
+  <si>
+    <t>1. 点击已分配用户的角色删除按钮
+2. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>系统给出对应提示不允许删除或进行级联处理，数据一致</t>
+  </si>
+  <si>
+    <t>ROLE-017</t>
+  </si>
+  <si>
+    <t>分配菜单权限树形勾选-保存后生效</t>
+  </si>
+  <si>
+    <t>列表存在对应角色</t>
+  </si>
+  <si>
+    <t>1. 点击某角色分配权限按钮
+2. 在树形结构勾选菜单与按钮权限
+3. 点击保存</t>
+  </si>
+  <si>
+    <t>保存成功，权限配置生效，提示保存成功</t>
+  </si>
+  <si>
+    <t>ROLE-018</t>
+  </si>
+  <si>
+    <t>全选取消全选-功能正常</t>
+  </si>
+  <si>
+    <t>已打开权限分配树形弹窗</t>
+  </si>
+  <si>
+    <t>1. 点击全选按钮
+2. 查看勾选状态
+3. 点击取消全选按钮
+4. 查看勾选状态</t>
+  </si>
+  <si>
+    <t>全选时所有菜单按钮均勾选，取消全选时所有勾选清空</t>
+  </si>
+  <si>
+    <t>ROLE-019</t>
+  </si>
+  <si>
+    <t>父子级权限联动-勾选父自动勾选子</t>
+  </si>
+  <si>
+    <t>1. 勾选某父级菜单
+2. 查看子菜单勾选状态</t>
+  </si>
+  <si>
+    <t>勾选父菜单时自动勾选其下所有子菜单</t>
+  </si>
+  <si>
+    <t>ROLE-020</t>
+  </si>
+  <si>
+    <t>取消子菜单不影响父级-联动正常</t>
+  </si>
+  <si>
+    <t>已勾选父子菜单权限</t>
+  </si>
+  <si>
+    <t>1. 取消勾选某子菜单
+2. 查看父菜单勾选状态</t>
+  </si>
+  <si>
+    <t>取消子菜单后父菜单勾选状态保持不变</t>
+  </si>
+  <si>
+    <t>ROLE-021</t>
+  </si>
+  <si>
+    <t>角色分配用户-用户权限同步变化</t>
+  </si>
+  <si>
+    <t>列表存在对应角色与用户</t>
+  </si>
+  <si>
+    <t>1. 点击某角色分配用户按钮
+2. 添加对应用户并保存
+3. 移除对应用户并保存
+4. 验证用户权限</t>
+  </si>
+  <si>
+    <t>添加用户后该用户获得对应权限，移除用户后该用户权限同步移除</t>
+  </si>
+  <si>
+    <t>ROLE-022</t>
+  </si>
+  <si>
+    <t>数据权限配置全部数据范围-生效正常</t>
+  </si>
+  <si>
+    <t>1. 点击某角色数据权限按钮
+2. 数据范围选择「全部」
+3. 保存
+4. 使用该角色账号查询数据</t>
+  </si>
+  <si>
+    <t>该角色账号可查询全部数据</t>
+  </si>
+  <si>
+    <t>ROLE-023</t>
+  </si>
+  <si>
+    <t>数据权限配置本部门数据范围-生效正常</t>
+  </si>
+  <si>
+    <t>列表存在对应角色且角色账号有所属部门</t>
+  </si>
+  <si>
+    <t>1. 点击某角色数据权限按钮
+2. 数据范围选择「本部门」
+3. 保存
+4. 使用该角色账号查询数据</t>
+  </si>
+  <si>
+    <t>该角色账号仅可查询本部门数据</t>
+  </si>
+  <si>
+    <t>ROLE-024</t>
+  </si>
+  <si>
+    <t>数据权限配置本人数据范围-生效正常</t>
+  </si>
+  <si>
+    <t>1. 点击某角色数据权限按钮
+2. 数据范围选择「本人」
+3. 保存
+4. 使用该角色账号查询数据</t>
+  </si>
+  <si>
+    <t>该角色账号仅可查询本人相关数据</t>
+  </si>
+  <si>
+    <t>MENU-001</t>
+  </si>
+  <si>
+    <t>菜单管理模块</t>
+  </si>
+  <si>
+    <t>菜单树形列表字段完整展示-字段齐全</t>
+  </si>
+  <si>
+    <t>已登录且有菜单管理查看权限</t>
+  </si>
+  <si>
+    <t>1. 进入菜单管理列表页
+2. 检查列表字段</t>
+  </si>
+  <si>
+    <t>列表完整展示菜单名称、图标、排序、类型、权限标识、路由地址、状态、操作列</t>
+  </si>
+  <si>
+    <t>MENU-002</t>
+  </si>
+  <si>
+    <t>树形展开折叠功能-正常</t>
+  </si>
+  <si>
+    <t>已进入菜单管理列表页且存在多级菜单</t>
+  </si>
+  <si>
+    <t>1. 点击树形节点展开按钮
+2. 点击折叠按钮</t>
+  </si>
+  <si>
+    <t>树形结构展开显示子菜单，折叠隐藏子菜单，功能正常</t>
+  </si>
+  <si>
+    <t>MENU-003</t>
+  </si>
+  <si>
+    <t>已进入菜单管理列表页</t>
+  </si>
+  <si>
+    <t>菜单名称、状态筛选、查询、重置按钮均正常展示</t>
+  </si>
+  <si>
+    <t>MENU-004</t>
+  </si>
+  <si>
+    <t>菜单名称模糊查询-正常过滤</t>
+  </si>
+  <si>
+    <t>列表存在多条菜单数据</t>
+  </si>
+  <si>
+    <t>1. 在查询区菜单名称输入部分关键字
+2. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表正确过滤展示包含该关键字的菜单数据</t>
+  </si>
+  <si>
+    <t>MENU-005</t>
+  </si>
+  <si>
+    <t>状态筛选-正常过滤</t>
+  </si>
+  <si>
+    <t>列表存在正常与停用状态菜单</t>
+  </si>
+  <si>
+    <t>列表展示对应状态的菜单数据</t>
+  </si>
+  <si>
+    <t>MENU-006</t>
+  </si>
+  <si>
+    <t>树形结构层级展示-父子关系清晰</t>
+  </si>
+  <si>
+    <t>存在多级菜单数据</t>
+  </si>
+  <si>
+    <t>1. 进入菜单管理列表页
+2. 展开树形结构查看层级</t>
+  </si>
+  <si>
+    <t>树形结构层级展示正确，父子级关系清晰，缩进显示正确</t>
+  </si>
+  <si>
+    <t>MENU-007</t>
+  </si>
+  <si>
+    <t>新增目录类型菜单-提交成功</t>
+  </si>
+  <si>
+    <t>1. 点击新增按钮
+2. 类型选择目录
+3. 填写菜单名称、排序、图标、路由地址
+4. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交成功，列表新增对应目录数据，提示新增成功</t>
+  </si>
+  <si>
+    <t>MENU-008</t>
+  </si>
+  <si>
+    <t>新增菜单类型-提交成功</t>
+  </si>
+  <si>
+    <t>1. 点击新增按钮
+2. 类型选择菜单
+3. 填写菜单名称、权限标识、组件路径
+4. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交成功，列表新增对应菜单数据，提示新增成功</t>
+  </si>
+  <si>
+    <t>MENU-009</t>
+  </si>
+  <si>
+    <t>新增按钮类型-提交成功</t>
+  </si>
+  <si>
+    <t>1. 点击新增按钮
+2. 类型选择按钮
+3. 填写权限标识
+4. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交成功，列表新增对应按钮数据，提示新增成功</t>
+  </si>
+  <si>
+    <t>MENU-010</t>
+  </si>
+  <si>
+    <t>上级菜单树形选择-层级关系正确</t>
+  </si>
+  <si>
+    <t>已打开新增菜单弹窗且存在可选父级菜单</t>
+  </si>
+  <si>
+    <t>1. 在新增弹窗点击上级菜单选择
+2. 在树形选择器选择父级菜单
+3. 提交保存</t>
+  </si>
+  <si>
+    <t>上级菜单选择正常，保存后层级关系正确，新菜单作为所选父级的子级</t>
+  </si>
+  <si>
+    <t>MENU-011</t>
+  </si>
+  <si>
+    <t>必填项为空-对应提示</t>
+  </si>
+  <si>
+    <t>已打开新增菜单弹窗</t>
+  </si>
+  <si>
+    <t>1. 菜单名称等必填项留空
+2. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，对应必填项提示必填，不发起请求</t>
+  </si>
+  <si>
+    <t>MENU-012</t>
+  </si>
+  <si>
+    <t>菜单名称重复-拦截提示</t>
+  </si>
+  <si>
+    <t>已存在对应菜单名称</t>
+  </si>
+  <si>
+    <t>1. 点击新增按钮
+2. 输入已存在的菜单名称
+3. 填写其他合法项
+4. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，提示菜单名称重复，不新增数据</t>
+  </si>
+  <si>
+    <t>MENU-013</t>
+  </si>
+  <si>
+    <t>编辑菜单信息-提交后同步更新</t>
+  </si>
+  <si>
+    <t>列表存在可编辑菜单</t>
+  </si>
+  <si>
+    <t>1. 点击某菜单修改按钮
+2. 修改菜单名称、排序、图标等信息
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>MENU-014</t>
+  </si>
+  <si>
+    <t>删除无子菜单菜单-二次确认删除成功</t>
+  </si>
+  <si>
+    <t>列表存在无子菜单的可删除菜单</t>
+  </si>
+  <si>
+    <t>1. 点击某无子菜单菜单删除按钮
+2. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>删除成功，列表移除该菜单数据，提示删除成功</t>
+  </si>
+  <si>
+    <t>MENU-015</t>
+  </si>
+  <si>
+    <t>存在子菜单父级删除-提示先删除子菜单</t>
+  </si>
+  <si>
+    <t>列表存在带子菜单的父级菜单</t>
+  </si>
+  <si>
+    <t>1. 点击某带子菜单的父级菜单删除按钮
+2. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>系统拦截删除，提示存在子菜单需先删除子菜单</t>
+  </si>
+  <si>
+    <t>MENU-016</t>
+  </si>
+  <si>
+    <t>删除菜单后用户菜单列表同步移除-数据一致</t>
+  </si>
+  <si>
+    <t>列表存在已分配给用户的菜单</t>
+  </si>
+  <si>
+    <t>1. 删除某已分配给用户的菜单
+2. 使用关联用户账号登录查看菜单</t>
+  </si>
+  <si>
+    <t>删除成功后，对应用户的菜单列表同步移除该菜单</t>
+  </si>
+  <si>
+    <t>MENU-017</t>
+  </si>
+  <si>
+    <t>新增菜单权限标识-角色管理可见对应权限项</t>
+  </si>
+  <si>
+    <t>已新增带权限标识的菜单</t>
+  </si>
+  <si>
+    <t>1. 新增带权限标识的菜单
+2. 进入角色管理分配权限弹窗查看</t>
+  </si>
+  <si>
+    <t>角色管理权限树中可看到对应新增的权限项</t>
+  </si>
+  <si>
+    <t>MENU-018</t>
+  </si>
+  <si>
+    <t>为角色分配菜单后用户登录可见-权限生效</t>
+  </si>
+  <si>
+    <t>已为角色分配某菜单权限</t>
+  </si>
+  <si>
+    <t>1. 为某角色分配菜单权限并保存
+2. 使用该角色下用户账号登录
+3. 查看左侧菜单</t>
+  </si>
+  <si>
+    <t>对应用户登录后可见对应分配的菜单</t>
+  </si>
+  <si>
+    <t>MENU-019</t>
+  </si>
+  <si>
+    <t>按钮权限配置后-按钮按权限显示隐藏</t>
+  </si>
+  <si>
+    <t>已配置按钮权限并分配给角色</t>
+  </si>
+  <si>
+    <t>1. 配置某按钮权限标识并分配给角色
+2. 使用有权限账号登录查看按钮
+3. 使用无权限账号登录查看按钮</t>
+  </si>
+  <si>
+    <t>有权限账号可见对应按钮，无权限账号隐藏对应按钮</t>
+  </si>
+  <si>
+    <t>DEPT-001</t>
+  </si>
+  <si>
+    <t>部门管理模块</t>
+  </si>
+  <si>
+    <t>部门树形列表字段完整展示-字段齐全</t>
+  </si>
+  <si>
+    <t>已登录且有部门管理查看权限</t>
+  </si>
+  <si>
+    <t>1. 进入部门管理列表页
+2. 检查列表字段</t>
+  </si>
+  <si>
+    <t>列表完整展示部门名称、状态、排序、负责人、联系电话、操作列</t>
+  </si>
+  <si>
+    <t>DEPT-002</t>
+  </si>
+  <si>
+    <t>部门树形展开折叠功能-正常</t>
+  </si>
+  <si>
+    <t>已进入部门管理列表页且存在多级部门</t>
+  </si>
+  <si>
+    <t>树形结构展开显示子部门，折叠隐藏子部门，功能正常</t>
+  </si>
+  <si>
+    <t>DEPT-003</t>
+  </si>
+  <si>
+    <t>已进入部门管理列表页</t>
+  </si>
+  <si>
+    <t>部门名称、状态筛选、查询、重置按钮均正常展示</t>
+  </si>
+  <si>
+    <t>DEPT-004</t>
+  </si>
+  <si>
+    <t>部门名称模糊查询-正常过滤</t>
+  </si>
+  <si>
+    <t>列表存在多条部门数据</t>
+  </si>
+  <si>
+    <t>1. 在查询区部门名称输入部分关键字
+2. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表正确过滤展示包含该关键字的部门数据</t>
+  </si>
+  <si>
+    <t>DEPT-005</t>
+  </si>
+  <si>
+    <t>列表存在正常与停用状态部门</t>
+  </si>
+  <si>
+    <t>列表展示对应状态的部门数据</t>
+  </si>
+  <si>
+    <t>DEPT-006</t>
+  </si>
+  <si>
+    <t>存在多级部门数据</t>
+  </si>
+  <si>
+    <t>1. 进入部门管理列表页
+2. 展开树形结构查看层级</t>
+  </si>
+  <si>
+    <t>树形结构层级展示正确，父子部门关系清晰，缩进显示正确</t>
+  </si>
+  <si>
+    <t>DEPT-007</t>
+  </si>
+  <si>
+    <t>新增部门合法数据-提交成功</t>
+  </si>
+  <si>
+    <t>1. 点击新增按钮
+2. 填写部门名称、排序、负责人、电话、邮箱
+3. 选择上级部门与状态
+4. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交成功，部门树新增对应部门数据，提示新增成功</t>
+  </si>
+  <si>
+    <t>DEPT-008</t>
+  </si>
+  <si>
+    <t>部门名称为空-必填提示</t>
+  </si>
+  <si>
+    <t>已打开新增部门弹窗</t>
+  </si>
+  <si>
+    <t>1. 部门名称留空
+2. 填写其他必填项
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，部门名称必填提示，不发起请求</t>
+  </si>
+  <si>
+    <t>DEPT-009</t>
+  </si>
+  <si>
+    <t>同一层级部门名称重复-拦截提示</t>
+  </si>
+  <si>
+    <t>已存在同一层级下对应部门名称</t>
+  </si>
+  <si>
+    <t>1. 点击新增按钮
+2. 选择同一上级部门
+3. 输入已存在的部门名称
+4. 填写其他合法项
+5. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交失败，提示同一层级下部门名称重复，不新增数据</t>
+  </si>
+  <si>
+    <t>DEPT-010</t>
+  </si>
+  <si>
+    <t>上级部门树形选择器-正常可用</t>
+  </si>
+  <si>
+    <t>已打开新增部门弹窗且存在可选上级部门</t>
+  </si>
+  <si>
+    <t>1. 在新增弹窗点击上级部门选择
+2. 在树形选择器选择上级部门
+3. 提交保存</t>
+  </si>
+  <si>
+    <t>上级部门树形选择器正常可用，保存后层级关系正确</t>
+  </si>
+  <si>
+    <t>DEPT-011</t>
+  </si>
+  <si>
+    <t>已打开新增部门弹窗且已填写数据</t>
+  </si>
+  <si>
+    <t>DEPT-012</t>
+  </si>
+  <si>
+    <t>编辑部门信息-提交后列表更新</t>
+  </si>
+  <si>
+    <t>列表存在可编辑部门</t>
+  </si>
+  <si>
+    <t>1. 点击某部门修改按钮
+2. 修改部门信息
+3. 点击确定提交</t>
+  </si>
+  <si>
+    <t>提交成功，部门树对应记录信息同步更新，提示修改成功</t>
+  </si>
+  <si>
+    <t>DEPT-013</t>
+  </si>
+  <si>
+    <t>删除无子部门部门-二次确认删除成功</t>
+  </si>
+  <si>
+    <t>列表存在无子部门的可删除部门</t>
+  </si>
+  <si>
+    <t>1. 点击某无子部门部门删除按钮
+2. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>删除成功，部门树移除该部门数据，提示删除成功</t>
+  </si>
+  <si>
+    <t>DEPT-014</t>
+  </si>
+  <si>
+    <t>存在下级部门删除-拦截提示</t>
+  </si>
+  <si>
+    <t>列表存在带下级部门的父级部门</t>
+  </si>
+  <si>
+    <t>1. 点击某带下级部门的父级部门删除按钮
+2. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>系统拦截删除，提示存在下级部门不允许删除</t>
+  </si>
+  <si>
+    <t>DEPT-015</t>
+  </si>
+  <si>
+    <t>存在用户的部门删除-拦截提示</t>
+  </si>
+  <si>
+    <t>列表存在带用户的部门</t>
+  </si>
+  <si>
+    <t>1. 点击某带用户的部门删除按钮
+2. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>系统拦截删除，提示存在用户不允许删除</t>
+  </si>
+  <si>
+    <t>DEPT-016</t>
+  </si>
+  <si>
+    <t>删除后部门树同步更新-数据一致</t>
+  </si>
+  <si>
+    <t>列表存在可删除部门</t>
+  </si>
+  <si>
+    <t>1. 删除某无关联部门
+2. 查看部门树展示</t>
+  </si>
+  <si>
+    <t>删除成功后部门树同步更新，该部门从树中移除</t>
+  </si>
+  <si>
+    <t>LOG-001</t>
+  </si>
+  <si>
+    <t>系统日志模块</t>
+  </si>
+  <si>
+    <t>操作日志列表字段完整展示-字段齐全</t>
+  </si>
+  <si>
+    <t>已登录且有操作日志查看权限，存在操作日志数据</t>
+  </si>
+  <si>
+    <t>1. 进入操作日志列表页
+2. 检查列表字段</t>
+  </si>
+  <si>
+    <t>列表完整展示日志编号、系统模块、操作类型、方法名称、请求方式、操作人、操作状态、操作时间</t>
+  </si>
+  <si>
+    <t>LOG-002</t>
+  </si>
+  <si>
+    <t>操作日志查询条件完整-条件齐全</t>
+  </si>
+  <si>
+    <t>已进入操作日志列表页</t>
+  </si>
+  <si>
+    <t>操作模块、操作人、操作类型、状态、时间范围查询条件均正常展示</t>
+  </si>
+  <si>
+    <t>LOG-003</t>
+  </si>
+  <si>
+    <t>操作日志条件筛选查询-正常过滤</t>
+  </si>
+  <si>
+    <t>存在满足条件的操作日志数据</t>
+  </si>
+  <si>
+    <t>1. 在查询区输入操作模块、操作人等条件
+2. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表正确过滤展示满足条件的操作日志数据</t>
+  </si>
+  <si>
+    <t>LOG-004</t>
+  </si>
+  <si>
+    <t>操作日志时间范围筛选-生效正常</t>
+  </si>
+  <si>
+    <t>存在不同时间的操作日志数据</t>
+  </si>
+  <si>
+    <t>1. 在查询区选择起止时间范围
+2. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表展示所选时间范围内的操作日志数据，时间范围筛选生效</t>
+  </si>
+  <si>
+    <t>LOG-005</t>
+  </si>
+  <si>
+    <t>操作日志查看详情-展示完整参数</t>
+  </si>
+  <si>
+    <t>列表存在操作日志数据</t>
+  </si>
+  <si>
+    <t>1. 点击某日志操作列详情按钮
+2. 查看详情弹窗内容</t>
+  </si>
+  <si>
+    <t>详情弹窗展示完整请求参数、返回结果、异常信息</t>
+  </si>
+  <si>
+    <t>LOG-006</t>
+  </si>
+  <si>
+    <t>操作日志单条删除-二次确认删除成功</t>
+  </si>
+  <si>
+    <t>列表存在可删除操作日志</t>
+  </si>
+  <si>
+    <t>1. 点击某日志删除按钮
+2. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>删除成功，列表移除该条日志，提示删除成功</t>
+  </si>
+  <si>
+    <t>LOG-007</t>
+  </si>
+  <si>
+    <t>操作日志批量删除-删除成功</t>
+  </si>
+  <si>
+    <t>列表存在多条可删除操作日志</t>
+  </si>
+  <si>
+    <t>1. 勾选多条日志数据
+2. 点击批量删除按钮
+3. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>删除成功，所有选中日志均从列表移除，提示删除成功</t>
+  </si>
+  <si>
+    <t>LOG-008</t>
+  </si>
+  <si>
+    <t>操作日志清空全部-二次确认生效</t>
+  </si>
+  <si>
+    <t>1. 点击清空按钮
+2. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>清空成功，列表所有日志数据移除，提示清空成功</t>
+  </si>
+  <si>
+    <t>LOG-009</t>
+  </si>
+  <si>
+    <t>操作日志导出-Excel内容一致</t>
+  </si>
+  <si>
+    <t>1. 点击导出按钮
+2. 打开下载的Excel文件</t>
+  </si>
+  <si>
+    <t>成功下载Excel文件，内容与列表数据一致</t>
+  </si>
+  <si>
+    <t>LOG-010</t>
+  </si>
+  <si>
+    <t>操作日志分页功能-分页正常</t>
+  </si>
+  <si>
+    <t>操作日志数据量大于默认每页条数</t>
+  </si>
+  <si>
+    <t>1. 进入操作日志列表页
+2. 切换每页条数与页码</t>
+  </si>
+  <si>
+    <t>分页功能正常，每页条数切换生效，页码切换数据正确</t>
+  </si>
+  <si>
+    <t>LOG-011</t>
+  </si>
+  <si>
+    <t>登录日志列表字段完整展示-字段齐全</t>
+  </si>
+  <si>
+    <t>已登录且有登录日志查看权限，存在登录日志数据</t>
+  </si>
+  <si>
+    <t>1. 进入登录日志列表页
+2. 检查列表字段</t>
+  </si>
+  <si>
+    <t>列表完整展示日志编号、用户名称、登录IP、登录地点、浏览器、操作系统、登录状态、操作时间</t>
+  </si>
+  <si>
+    <t>LOG-012</t>
+  </si>
+  <si>
+    <t>登录日志查询条件完整-条件齐全</t>
+  </si>
+  <si>
+    <t>已进入登录日志列表页</t>
+  </si>
+  <si>
+    <t>用户名称、登录状态、时间范围查询条件均正常展示</t>
+  </si>
+  <si>
+    <t>LOG-013</t>
+  </si>
+  <si>
+    <t>登录日志条件筛选查询-正常过滤</t>
+  </si>
+  <si>
+    <t>存在满足条件的登录日志数据</t>
+  </si>
+  <si>
+    <t>1. 在查询区输入用户名称、选择登录状态、时间范围
+2. 点击查询按钮</t>
+  </si>
+  <si>
+    <t>列表正确过滤展示满足条件的登录日志数据</t>
+  </si>
+  <si>
+    <t>LOG-014</t>
+  </si>
+  <si>
+    <t>在线用户强退-强制用户下线</t>
+  </si>
+  <si>
+    <t>存在在线用户</t>
+  </si>
+  <si>
+    <t>1. 进入在线用户列表
+2. 点击某在线用户强退按钮
+3. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>强退成功，该用户被强制下线，原Token失效无法继续操作</t>
+  </si>
+  <si>
+    <t>LOG-015</t>
+  </si>
+  <si>
+    <t>账号锁定后手动解锁-解锁成功</t>
+  </si>
+  <si>
+    <t>存在被锁定的账号</t>
+  </si>
+  <si>
+    <t>1. 进入登录日志列表
+2. 找到锁定状态账号
+3. 点击解锁按钮
+4. 在二次确认框点击确认</t>
+  </si>
+  <si>
+    <t>解锁成功，账号恢复可登录状态，提示解锁成功</t>
+  </si>
+  <si>
+    <t>LOG-016</t>
+  </si>
+  <si>
+    <t>登录日志导出-导出正常</t>
+  </si>
+  <si>
+    <t>列表存在登录日志数据</t>
+  </si>
+  <si>
+    <t>LOG-017</t>
+  </si>
+  <si>
+    <t>登录日志分页功能-分页正常</t>
+  </si>
+  <si>
+    <t>登录日志数据量大于默认每页条数</t>
+  </si>
+  <si>
+    <t>1. 进入登录日志列表页
+2. 切换每页条数与页码</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="25">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFBF8F00"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,12 +2558,42 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF305496"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4E6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4E4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -370,12 +2782,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9DEE7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9DEE7"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9DEE7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9DEE7"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -478,157 +2905,174 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -682,7 +3126,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -691,10 +3135,77 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1770800</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>710400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1875300</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>298400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Watermark"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6799580" y="6399530"/>
+          <a:ext cx="2200275" cy="349885"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="b"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="r"/>
+          <a:r>
+            <a:rPr lang="zh-CN" sz="1600" dirty="0">
+              <a:solidFill>
+                <a:srgbClr val="808080">
+                  <a:alpha val="19999"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204"/>
+              <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="7" charset="-122"/>
+            </a:rPr>
+            <a:t>AI 生成</a:t>
+          </a:r>
+          <a:endParaRPr lang="zh-CN" sz="1600" dirty="0">
+            <a:solidFill>
+              <a:srgbClr val="808080">
+                <a:alpha val="19999"/>
+              </a:srgbClr>
+            </a:solidFill>
+            <a:latin typeface="Arial" panose="020B0604020202020204"/>
+            <a:ea typeface="宋体" panose="02010600030101010101" pitchFamily="7" charset="-122"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="WPS">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -702,39 +3213,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4874CB"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EE822F"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="F2BA02"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="75BD42"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="30C0B4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="E54C5E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0026E5"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="7E1FAD"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="WPS">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -766,7 +3277,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -801,135 +3311,171 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="WPS">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumOff val="17500"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:hueOff val="-2520000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr"/>
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:gradFill>
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="phClr">
-                  <a:hueOff val="-4200000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="phClr"/>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
-          </a:gradFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:schemeClr val="phClr">
-                <a:alpha val="60000"/>
-              </a:schemeClr>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -941,35 +3487,4826 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <dimension ref="A1:J150"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1" spans="1:10">
+      <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1" spans="1:10">
+      <c r="A5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1" spans="1:10">
+      <c r="A7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1" spans="1:10">
+      <c r="A9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1" spans="1:10">
+      <c r="A11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1" spans="1:10">
+      <c r="A13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1" spans="1:10">
+      <c r="A15" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1" spans="1:10">
+      <c r="A17" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1" spans="1:10">
+      <c r="A19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1" spans="1:10">
+      <c r="A21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" ht="60" customHeight="1" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="60" customHeight="1" spans="1:10">
+      <c r="A23" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1" spans="1:10">
+      <c r="A25" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1" spans="1:10">
+      <c r="A27" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1" spans="1:10">
+      <c r="A29" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1" spans="1:10">
+      <c r="A31" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1" spans="1:10">
+      <c r="A32" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1" spans="1:10">
+      <c r="A33" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1" spans="1:10">
+      <c r="A34" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1" spans="1:10">
+      <c r="A35" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1" spans="1:10">
+      <c r="A36" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1" spans="1:10">
+      <c r="A37" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1" spans="1:10">
+      <c r="A38" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1" spans="1:10">
+      <c r="A39" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1" spans="1:10">
+      <c r="A40" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1" spans="1:10">
+      <c r="A41" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1" spans="1:10">
+      <c r="A42" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" ht="60" customHeight="1" spans="1:10">
+      <c r="A43" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" ht="60" customHeight="1" spans="1:10">
+      <c r="A44" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1" spans="1:10">
+      <c r="A45" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" ht="60" customHeight="1" spans="1:10">
+      <c r="A46" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1" spans="1:10">
+      <c r="A47" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" ht="60" customHeight="1" spans="1:10">
+      <c r="A48" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1" spans="1:10">
+      <c r="A49" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1" spans="1:10">
+      <c r="A50" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1" spans="1:10">
+      <c r="A51" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1" spans="1:10">
+      <c r="A52" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1" spans="1:10">
+      <c r="A53" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1" spans="1:10">
+      <c r="A54" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1" spans="1:10">
+      <c r="A55" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1" spans="1:10">
+      <c r="A56" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1" spans="1:10">
+      <c r="A57" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1" spans="1:10">
+      <c r="A58" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1" spans="1:10">
+      <c r="A59" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" ht="60" customHeight="1" spans="1:10">
+      <c r="A60" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1" spans="1:10">
+      <c r="A61" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" ht="60" customHeight="1" spans="1:10">
+      <c r="A62" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" ht="60" customHeight="1" spans="1:10">
+      <c r="A63" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="G63" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" ht="60" customHeight="1" spans="1:10">
+      <c r="A64" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" ht="60" customHeight="1" spans="1:10">
+      <c r="A65" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="G65" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1" spans="1:10">
+      <c r="A66" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1" spans="1:10">
+      <c r="A67" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="G67" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1" spans="1:10">
+      <c r="A68" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1" spans="1:10">
+      <c r="A69" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="G69" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1" spans="1:10">
+      <c r="A70" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1" spans="1:10">
+      <c r="A71" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" ht="60" customHeight="1" spans="1:10">
+      <c r="A72" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" ht="60" customHeight="1" spans="1:10">
+      <c r="A73" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1" spans="1:10">
+      <c r="A74" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" ht="60" customHeight="1" spans="1:10">
+      <c r="A75" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G75" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" ht="60" customHeight="1" spans="1:10">
+      <c r="A76" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" ht="60" customHeight="1" spans="1:10">
+      <c r="A77" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="G77" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" ht="60" customHeight="1" spans="1:10">
+      <c r="A78" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" ht="60" customHeight="1" spans="1:10">
+      <c r="A79" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" ht="60" customHeight="1" spans="1:10">
+      <c r="A80" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" ht="60" customHeight="1" spans="1:10">
+      <c r="A81" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" ht="60" customHeight="1" spans="1:10">
+      <c r="A82" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" ht="60" customHeight="1" spans="1:10">
+      <c r="A83" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" ht="60" customHeight="1" spans="1:10">
+      <c r="A84" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" ht="60" customHeight="1" spans="1:10">
+      <c r="A85" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="86" ht="60" customHeight="1" spans="1:10">
+      <c r="A86" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" ht="60" customHeight="1" spans="1:10">
+      <c r="A87" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="88" ht="60" customHeight="1" spans="1:10">
+      <c r="A88" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" ht="60" customHeight="1" spans="1:10">
+      <c r="A89" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" ht="60" customHeight="1" spans="1:10">
+      <c r="A90" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="91" ht="60" customHeight="1" spans="1:10">
+      <c r="A91" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" ht="60" customHeight="1" spans="1:10">
+      <c r="A92" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" ht="60" customHeight="1" spans="1:10">
+      <c r="A93" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" ht="60" customHeight="1" spans="1:10">
+      <c r="A94" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" ht="60" customHeight="1" spans="1:10">
+      <c r="A95" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" ht="60" customHeight="1" spans="1:10">
+      <c r="A96" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" ht="60" customHeight="1" spans="1:10">
+      <c r="A97" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" ht="60" customHeight="1" spans="1:10">
+      <c r="A98" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" ht="60" customHeight="1" spans="1:10">
+      <c r="A99" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="F99" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="G99" s="5" t="s">
+        <v>464</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" ht="60" customHeight="1" spans="1:10">
+      <c r="A100" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="101" ht="60" customHeight="1" spans="1:10">
+      <c r="A101" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" s="5" t="s">
+        <v>471</v>
+      </c>
+      <c r="F101" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G101" s="5" t="s">
+        <v>472</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" ht="60" customHeight="1" spans="1:10">
+      <c r="A102" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" ht="60" customHeight="1" spans="1:10">
+      <c r="A103" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E103" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="F103" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="G103" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="H103" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="104" ht="60" customHeight="1" spans="1:10">
+      <c r="A104" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" ht="60" customHeight="1" spans="1:10">
+      <c r="A105" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="G105" s="5" t="s">
+        <v>490</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J105" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="106" ht="60" customHeight="1" spans="1:10">
+      <c r="A106" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" ht="60" customHeight="1" spans="1:10">
+      <c r="A107" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="D107" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="G107" s="5" t="s">
+        <v>498</v>
+      </c>
+      <c r="H107" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J107" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="108" ht="60" customHeight="1" spans="1:10">
+      <c r="A108" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="109" ht="60" customHeight="1" spans="1:10">
+      <c r="A109" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="G109" s="5" t="s">
+        <v>508</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="110" ht="60" customHeight="1" spans="1:10">
+      <c r="A110" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" ht="60" customHeight="1" spans="1:10">
+      <c r="A111" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J111" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" ht="60" customHeight="1" spans="1:10">
+      <c r="A112" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" ht="60" customHeight="1" spans="1:10">
+      <c r="A113" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="G113" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J113" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="114" ht="60" customHeight="1" spans="1:10">
+      <c r="A114" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="115" ht="60" customHeight="1" spans="1:10">
+      <c r="A115" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="G115" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="116" ht="60" customHeight="1" spans="1:10">
+      <c r="A116" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="117" ht="60" customHeight="1" spans="1:10">
+      <c r="A117" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="G117" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="H117" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I117" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="118" ht="60" customHeight="1" spans="1:10">
+      <c r="A118" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" ht="60" customHeight="1" spans="1:10">
+      <c r="A119" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>556</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="H119" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I119" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J119" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" ht="60" customHeight="1" spans="1:10">
+      <c r="A120" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="121" ht="60" customHeight="1" spans="1:10">
+      <c r="A121" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="G121" s="5" t="s">
+        <v>565</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I121" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J121" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="122" ht="60" customHeight="1" spans="1:10">
+      <c r="A122" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="123" ht="60" customHeight="1" spans="1:10">
+      <c r="A123" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>571</v>
+      </c>
+      <c r="G123" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="H123" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J123" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" ht="60" customHeight="1" spans="1:10">
+      <c r="A124" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="125" ht="60" customHeight="1" spans="1:10">
+      <c r="A125" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E125" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G125" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I125" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J125" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="126" ht="60" customHeight="1" spans="1:10">
+      <c r="A126" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="127" ht="60" customHeight="1" spans="1:10">
+      <c r="A127" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E127" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="G127" s="5" t="s">
+        <v>591</v>
+      </c>
+      <c r="H127" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J127" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="128" ht="60" customHeight="1" spans="1:10">
+      <c r="A128" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" ht="60" customHeight="1" spans="1:10">
+      <c r="A129" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="B129" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="F129" s="5" t="s">
+        <v>597</v>
+      </c>
+      <c r="G129" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I129" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J129" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" ht="60" customHeight="1" spans="1:10">
+      <c r="A130" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="131" ht="60" customHeight="1" spans="1:10">
+      <c r="A131" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="F131" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="G131" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="H131" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I131" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J131" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="132" ht="60" customHeight="1" spans="1:10">
+      <c r="A132" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="133" ht="60" customHeight="1" spans="1:10">
+      <c r="A133" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="B133" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="C133" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E133" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="F133" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="G133" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="H133" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I133" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J133" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="134" ht="60" customHeight="1" spans="1:10">
+      <c r="A134" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" ht="60" customHeight="1" spans="1:10">
+      <c r="A135" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="F135" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G135" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="H135" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I135" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J135" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="136" ht="60" customHeight="1" spans="1:10">
+      <c r="A136" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" ht="60" customHeight="1" spans="1:10">
+      <c r="A137" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E137" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="G137" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="H137" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I137" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J137" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="138" ht="60" customHeight="1" spans="1:10">
+      <c r="A138" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="139" ht="60" customHeight="1" spans="1:10">
+      <c r="A139" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E139" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="G139" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="H139" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I139" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J139" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="140" ht="60" customHeight="1" spans="1:10">
+      <c r="A140" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="141" ht="60" customHeight="1" spans="1:10">
+      <c r="A141" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="B141" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E141" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="F141" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="G141" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="H141" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J141" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="142" ht="60" customHeight="1" spans="1:10">
+      <c r="A142" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" ht="60" customHeight="1" spans="1:10">
+      <c r="A143" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E143" s="5" t="s">
+        <v>664</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>665</v>
+      </c>
+      <c r="G143" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="H143" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J143" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" ht="60" customHeight="1" spans="1:10">
+      <c r="A144" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" ht="60" customHeight="1" spans="1:10">
+      <c r="A145" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="F145" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="G145" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J145" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" ht="60" customHeight="1" spans="1:10">
+      <c r="A146" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="147" ht="60" customHeight="1" spans="1:10">
+      <c r="A147" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E147" s="5" t="s">
+        <v>683</v>
+      </c>
+      <c r="F147" s="5" t="s">
+        <v>684</v>
+      </c>
+      <c r="G147" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="H147" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I147" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J147" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="148" ht="60" customHeight="1" spans="1:10">
+      <c r="A148" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="149" ht="60" customHeight="1" spans="1:10">
+      <c r="A149" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="B149" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>693</v>
+      </c>
+      <c r="F149" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="G149" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="H149" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J149" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="150" ht="60" customHeight="1" spans="1:10">
+      <c r="A150" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J150">
+    <extLst/>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>